--- a/HMS-TAX_Updated/HMS-TAX/bin/Debug/Reports/rpt_po_summary.xlsx
+++ b/HMS-TAX_Updated/HMS-TAX/bin/Debug/Reports/rpt_po_summary.xlsx
@@ -40,13 +40,14 @@
     <t>Items</t>
   </si>
   <si>
-    <t>Exp</t>
-  </si>
-  <si>
     <t>PO ID</t>
   </si>
   <si>
     <t>Purchase Order Summary</t>
+  </si>
+  <si>
+    <t>Other
+Cost</t>
   </si>
 </sst>
 </file>
@@ -54,7 +55,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -86,13 +87,6 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
-      <color rgb="FF002060"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF002060"/>
       <name val="Calibri"/>
@@ -105,6 +99,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF002060"/>
+      <name val="Cooper Black"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -156,9 +157,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -177,17 +178,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -196,13 +197,13 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -217,18 +218,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -541,9 +545,10 @@
     <col min="3" max="3" width="15.28515625" style="6" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" style="6" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" style="22" customWidth="1"/>
-    <col min="6" max="7" width="6.7109375" style="15" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" style="14" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="15" customWidth="1"/>
+    <col min="6" max="6" width="7" style="15" customWidth="1"/>
+    <col min="7" max="7" width="8" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="14" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" style="15" customWidth="1"/>
     <col min="10" max="10" width="16.28515625" style="6" customWidth="1"/>
     <col min="11" max="11" width="16.42578125" style="4" bestFit="1" customWidth="1"/>
   </cols>
@@ -561,28 +566,28 @@
     </row>
     <row r="2" spans="2:11" customFormat="1" ht="13.15" customHeight="1">
       <c r="B2" s="19"/>
-      <c r="C2" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
+      <c r="C2" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="2:11" customFormat="1" ht="16.899999999999999" customHeight="1">
       <c r="B3" s="19"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="2:11" customFormat="1" ht="21" customHeight="1">
@@ -600,12 +605,12 @@
       <c r="I4" s="17"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="2:11" customFormat="1" ht="23.45" customHeight="1">
+    <row r="5" spans="2:11" customFormat="1" ht="31.5">
       <c r="B5" s="21" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>6</v>
@@ -616,8 +621,8 @@
       <c r="F5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="12" t="s">
-        <v>8</v>
+      <c r="G5" s="26" t="s">
+        <v>10</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>4</v>
